--- a/features.xlsx
+++ b/features.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\uni\python\TBA_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C916AF3-8E49-4078-B912-EE87FBE693A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC94B842-A365-4586-8512-A039187DC053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="10272" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="features" sheetId="1" r:id="rId1"/>
+    <sheet name="example data" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="121">
   <si>
     <t>feature</t>
   </si>
@@ -93,9 +94,6 @@
     <t>station_related</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
     <t>feature engineering</t>
   </si>
   <si>
@@ -126,9 +124,6 @@
     <t xml:space="preserve">planned_depature - planned_arrival </t>
   </si>
   <si>
-    <t>weather data</t>
-  </si>
-  <si>
     <t>sequence_related</t>
   </si>
   <si>
@@ -183,9 +178,6 @@
     <t>stops_total</t>
   </si>
   <si>
-    <t>ride_related_history</t>
-  </si>
-  <si>
     <t>station_related_history</t>
   </si>
   <si>
@@ -207,21 +199,6 @@
     <t>start / stopover / destination</t>
   </si>
   <si>
-    <t>groub by train_name and give delay (mean)</t>
-  </si>
-  <si>
-    <t>groub by train_name and give delay (sd)</t>
-  </si>
-  <si>
-    <t>hist_delay_rate_train_name</t>
-  </si>
-  <si>
-    <t>hist_delay_sd_train_name</t>
-  </si>
-  <si>
-    <t>hist_delay_avg_train_name</t>
-  </si>
-  <si>
     <t>hist_delay_avg_station * day</t>
   </si>
   <si>
@@ -252,26 +229,173 @@
     <t>availability historical data</t>
   </si>
   <si>
-    <t>availability new data</t>
-  </si>
-  <si>
-    <t>comment feature engineering</t>
-  </si>
-  <si>
-    <t>only needed for grouping</t>
-  </si>
-  <si>
     <t>dataset</t>
   </si>
   <si>
-    <t>trains delay &gt; 5 minutes / all trains</t>
+    <t>not needed</t>
+  </si>
+  <si>
+    <t>? (@eddi)</t>
+  </si>
+  <si>
+    <t>variable not needed</t>
+  </si>
+  <si>
+    <t>other comments</t>
+  </si>
+  <si>
+    <t>api_bahn</t>
+  </si>
+  <si>
+    <t>api_bahn?</t>
+  </si>
+  <si>
+    <t>information on all stops needed</t>
+  </si>
+  <si>
+    <t>information on starting station needed</t>
+  </si>
+  <si>
+    <t>information on destination station needed</t>
+  </si>
+  <si>
+    <t>information above needed</t>
+  </si>
+  <si>
+    <t>can be still relevant for predicition (models hidden associations that are not captured by other features, i.e., priorization of certain trains, problem: new train names? + NJ has no unique train names</t>
+  </si>
+  <si>
+    <t>take from time start station</t>
+  </si>
+  <si>
+    <t>availability api data</t>
+  </si>
+  <si>
+    <t>route_related_history</t>
+  </si>
+  <si>
+    <t>hist_delay_avg_route</t>
+  </si>
+  <si>
+    <t>hist_delay_sd_route</t>
+  </si>
+  <si>
+    <t>group all connections that have common start station and current station (trains coming from X, how much delay do they have at Y?)</t>
+  </si>
+  <si>
+    <t>from historical data (saved from training)</t>
+  </si>
+  <si>
+    <t>weather api</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has to be found out </t>
+  </si>
+  <si>
+    <t>comments api data</t>
+  </si>
+  <si>
+    <t>comments historical data</t>
+  </si>
+  <si>
+    <t>needed for grouping</t>
+  </si>
+  <si>
+    <t>ICE 920</t>
+  </si>
+  <si>
+    <t>ICE 921</t>
+  </si>
+  <si>
+    <t>ICE 922</t>
+  </si>
+  <si>
+    <t>ICE 923</t>
+  </si>
+  <si>
+    <t>ICE 924</t>
+  </si>
+  <si>
+    <t>ICE 925</t>
+  </si>
+  <si>
+    <t>ICE 926</t>
+  </si>
+  <si>
+    <t>ICE</t>
+  </si>
+  <si>
+    <t>Frankfurt</t>
+  </si>
+  <si>
+    <t>Hamburg-Altona</t>
+  </si>
+  <si>
+    <t>Halt 1</t>
+  </si>
+  <si>
+    <t>Halt 2</t>
+  </si>
+  <si>
+    <t>Halt 3</t>
+  </si>
+  <si>
+    <t>Halt 4</t>
+  </si>
+  <si>
+    <t>Halt 5</t>
+  </si>
+  <si>
+    <t>arrival_planned</t>
+  </si>
+  <si>
+    <t>arrival_real</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>depature_planned</t>
+  </si>
+  <si>
+    <t>depature_real</t>
+  </si>
+  <si>
+    <t>ZEIT</t>
+  </si>
+  <si>
+    <t>delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">would be planned_depature - planned_arrival </t>
+  </si>
+  <si>
+    <t>not so important</t>
+  </si>
+  <si>
+    <t>we can leave the weather for every station out, this would reduce complexity because we then only have 2 weather api calls for every train ride</t>
+  </si>
+  <si>
+    <t>time_current_planned</t>
+  </si>
+  <si>
+    <t>planned_depature</t>
+  </si>
+  <si>
+    <t>info on start/destination needed</t>
+  </si>
+  <si>
+    <t>info on position of station_current in ride needed</t>
+  </si>
+  <si>
+    <t>above needed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -287,16 +411,40 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -319,14 +467,272 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -607,57 +1013,71 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="31.83984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.20703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.47265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="42.83984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.41796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.83984375" customWidth="1"/>
+    <col min="4" max="4" width="22.5234375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.26171875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="49.7890625" customWidth="1"/>
+    <col min="7" max="7" width="39.89453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="66.578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="1" t="s">
+      <c r="D1" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1" t="s">
+      <c r="D2" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -666,14 +1086,20 @@
       <c r="C3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="6" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -682,14 +1108,18 @@
       <c r="C4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" s="1"/>
+      <c r="D4" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>72</v>
+      </c>
       <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
+      <c r="G4" s="1"/>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -698,17 +1128,23 @@
       <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="1"/>
+      <c r="D5" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>72</v>
+      </c>
       <c r="F5" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
@@ -716,15 +1152,21 @@
       <c r="C6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="1"/>
+      <c r="D6" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>72</v>
+      </c>
       <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
-        <v>51</v>
+      <c r="G6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -732,16 +1174,22 @@
       <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="1"/>
+      <c r="D7" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>22</v>
+      </c>
       <c r="F7" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -750,17 +1198,23 @@
       <c r="C8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" s="1"/>
+      <c r="D8" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>22</v>
+      </c>
       <c r="F8" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>13</v>
@@ -768,16 +1222,22 @@
       <c r="C9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="1"/>
+      <c r="D9" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>22</v>
+      </c>
       <c r="F9" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -786,16 +1246,22 @@
       <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="1"/>
+      <c r="D10" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>22</v>
+      </c>
       <c r="F10" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -804,14 +1270,22 @@
       <c r="C11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1" t="s">
+      <c r="D11" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -820,14 +1294,22 @@
       <c r="C12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1" t="s">
+      <c r="D12" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -836,14 +1318,22 @@
       <c r="C13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="1" t="s">
+      <c r="D13" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -852,14 +1342,22 @@
       <c r="C14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="1" t="s">
+      <c r="D14" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H14" s="7"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -868,14 +1366,22 @@
       <c r="C15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="1" t="s">
+      <c r="D15" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -884,437 +1390,896 @@
       <c r="C16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="1"/>
+      <c r="D16" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>86</v>
+      </c>
       <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="1" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A17" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B18" s="1" t="s">
+      <c r="D17" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="9"/>
+    </row>
+    <row r="18" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A20" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="1" t="s">
+      <c r="C20" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H20" s="9"/>
+    </row>
+    <row r="21" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="23"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="1" t="s">
+      <c r="D24" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="17" t="s">
         <v>73</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="1" t="s">
-        <v>72</v>
+        <v>21</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F26" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="1" t="s">
-        <v>71</v>
+        <v>51</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H26" s="7"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F27" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="1" t="s">
-        <v>65</v>
+        <v>52</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H27" s="7"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1" t="s">
+      <c r="G28" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H28" s="7"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="6" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F29" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="1" t="s">
-        <v>67</v>
+        <v>54</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H29" s="7"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F30" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="1" t="s">
-        <v>68</v>
+        <v>54</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H30" s="7"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E31" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F31" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H31" s="7"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E32" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="D32" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F32" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="1" t="s">
-        <v>70</v>
+        <v>55</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H32" s="7"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E33" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F33" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H33" s="7"/>
+    </row>
+    <row r="34" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A34" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H34" s="9"/>
+    </row>
+    <row r="35" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="10"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="1" t="s">
-        <v>35</v>
+      <c r="C36" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="1" t="s">
-        <v>37</v>
+      <c r="G37" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="H37" s="7"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E38" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>22</v>
+      </c>
       <c r="F38" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H38" s="7"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E39" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" s="26" t="s">
+        <v>22</v>
+      </c>
       <c r="F39" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H39" s="7"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E40" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="D40" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="26" t="s">
+        <v>22</v>
+      </c>
       <c r="F40" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H40" s="7"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E41" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="D41" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41" s="26" t="s">
+        <v>22</v>
+      </c>
       <c r="F41" s="1" t="s">
-        <v>48</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H41" s="7"/>
+    </row>
+    <row r="42" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A42" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="H42" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E59CFC8-413C-463C-B177-BDA848B5E119}">
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="19.62890625" customWidth="1"/>
+    <col min="5" max="6" width="13.734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.9453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.1015625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7890625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1" t="s">
+        <v>110</v>
+      </c>
+      <c r="K1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J2" t="s">
+        <v>111</v>
+      </c>
+      <c r="K2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J3" t="s">
+        <v>111</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I4" t="s">
+        <v>111</v>
+      </c>
+      <c r="J4" t="s">
+        <v>111</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" t="s">
+        <v>111</v>
+      </c>
+      <c r="H5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I5" t="s">
+        <v>111</v>
+      </c>
+      <c r="J5" t="s">
+        <v>111</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G6" t="s">
+        <v>111</v>
+      </c>
+      <c r="H6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I6" t="s">
+        <v>111</v>
+      </c>
+      <c r="J6" t="s">
+        <v>111</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I7" t="s">
+        <v>111</v>
+      </c>
+      <c r="J7" t="s">
+        <v>111</v>
+      </c>
+      <c r="K7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" t="s">
+        <v>111</v>
+      </c>
+      <c r="H8" t="s">
+        <v>111</v>
+      </c>
+      <c r="I8" t="s">
+        <v>108</v>
+      </c>
+      <c r="J8" t="s">
+        <v>108</v>
+      </c>
+      <c r="K8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="29"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="30"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="30"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/features.xlsx
+++ b/features.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\uni\python\TBA_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC94B842-A365-4586-8512-A039187DC053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F57014-534C-42C9-A837-6BB0D22BF2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="10272" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="115">
   <si>
     <t>feature</t>
   </si>
@@ -302,24 +302,6 @@
   </si>
   <si>
     <t>ICE 920</t>
-  </si>
-  <si>
-    <t>ICE 921</t>
-  </si>
-  <si>
-    <t>ICE 922</t>
-  </si>
-  <si>
-    <t>ICE 923</t>
-  </si>
-  <si>
-    <t>ICE 924</t>
-  </si>
-  <si>
-    <t>ICE 925</t>
-  </si>
-  <si>
-    <t>ICE 926</t>
   </si>
   <si>
     <t>ICE</t>
@@ -699,7 +681,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -720,17 +702,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
   </cellXfs>
@@ -1128,7 +1105,7 @@
       <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="23" t="s">
         <v>22</v>
       </c>
       <c r="E5" s="17" t="s">
@@ -1174,10 +1151,10 @@
       <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="26" t="s">
+      <c r="D7" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -1198,10 +1175,10 @@
       <c r="C8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="26" t="s">
+      <c r="D8" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -1222,10 +1199,10 @@
       <c r="C9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="26" t="s">
+      <c r="D9" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -1246,10 +1223,10 @@
       <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="26" t="s">
+      <c r="D10" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -1270,10 +1247,10 @@
       <c r="C11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="26" t="s">
+      <c r="D11" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -1294,10 +1271,10 @@
       <c r="C12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="26" t="s">
+      <c r="D12" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -1318,10 +1295,10 @@
       <c r="C13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="26" t="s">
+      <c r="D13" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -1342,10 +1319,10 @@
       <c r="C14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="26" t="s">
+      <c r="D14" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -1366,10 +1343,10 @@
       <c r="C15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="26" t="s">
+      <c r="D15" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -1424,8 +1401,8 @@
       <c r="A18" s="10"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
@@ -1440,10 +1417,10 @@
       <c r="C19" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D19" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" s="24" t="s">
+      <c r="D19" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>68</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -1464,10 +1441,10 @@
       <c r="C20" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="25" t="s">
+      <c r="D20" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>68</v>
       </c>
       <c r="F20" s="8" t="s">
@@ -1509,8 +1486,8 @@
       <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="21" t="s">
-        <v>116</v>
+      <c r="A23" s="20" t="s">
+        <v>110</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>13</v>
@@ -1518,17 +1495,17 @@
       <c r="C23" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="31" t="s">
+      <c r="E23" s="26" t="s">
         <v>72</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G23" s="2"/>
-      <c r="H23" s="23"/>
+      <c r="H23" s="22"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="6" t="s">
@@ -1540,7 +1517,7 @@
       <c r="C24" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="26" t="s">
+      <c r="D24" s="23" t="s">
         <v>22</v>
       </c>
       <c r="E24" s="17" t="s">
@@ -1550,10 +1527,10 @@
         <v>31</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1575,7 +1552,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="7" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1588,7 +1565,7 @@
       <c r="C26" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="26" t="s">
+      <c r="D26" s="23" t="s">
         <v>22</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -1612,7 +1589,7 @@
       <c r="C27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="26" t="s">
+      <c r="D27" s="23" t="s">
         <v>22</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -1636,7 +1613,7 @@
       <c r="C28" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="26" t="s">
+      <c r="D28" s="23" t="s">
         <v>22</v>
       </c>
       <c r="E28" s="1" t="s">
@@ -1660,7 +1637,7 @@
       <c r="C29" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="26" t="s">
+      <c r="D29" s="23" t="s">
         <v>22</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -1684,7 +1661,7 @@
       <c r="C30" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="26" t="s">
+      <c r="D30" s="23" t="s">
         <v>22</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -1708,7 +1685,7 @@
       <c r="C31" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D31" s="26" t="s">
+      <c r="D31" s="23" t="s">
         <v>22</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -1732,7 +1709,7 @@
       <c r="C32" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D32" s="26" t="s">
+      <c r="D32" s="23" t="s">
         <v>22</v>
       </c>
       <c r="E32" s="1" t="s">
@@ -1756,7 +1733,7 @@
       <c r="C33" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D33" s="26" t="s">
+      <c r="D33" s="23" t="s">
         <v>22</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -1780,7 +1757,7 @@
       <c r="C34" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="28" t="s">
+      <c r="D34" s="25" t="s">
         <v>22</v>
       </c>
       <c r="E34" s="8" t="s">
@@ -1801,7 +1778,7 @@
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
-      <c r="G35" s="32"/>
+      <c r="G35" s="27"/>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1814,17 +1791,17 @@
       <c r="C36" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D36" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E36" s="27" t="s">
+      <c r="D36" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="24" t="s">
         <v>22</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="H36" s="5"/>
     </row>
@@ -1838,17 +1815,17 @@
       <c r="C37" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E37" s="26" t="s">
+      <c r="D37" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="20" t="s">
-        <v>119</v>
+      <c r="G37" s="10" t="s">
+        <v>113</v>
       </c>
       <c r="H37" s="7"/>
     </row>
@@ -1862,10 +1839,10 @@
       <c r="C38" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E38" s="26" t="s">
+      <c r="D38" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F38" s="1" t="s">
@@ -1886,10 +1863,10 @@
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E39" s="26" t="s">
+      <c r="D39" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F39" s="1" t="s">
@@ -1910,10 +1887,10 @@
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E40" s="26" t="s">
+      <c r="D40" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F40" s="1" t="s">
@@ -1934,17 +1911,17 @@
       <c r="C41" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D41" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E41" s="26" t="s">
+      <c r="D41" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="H41" s="7"/>
     </row>
@@ -1958,17 +1935,17 @@
       <c r="C42" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D42" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E42" s="28" t="s">
+      <c r="D42" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" s="25" t="s">
         <v>22</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="H42" s="9"/>
     </row>
@@ -1979,7 +1956,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E59CFC8-413C-463C-B177-BDA848B5E119}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="19.62890625" customWidth="1"/>
@@ -2009,19 +1986,19 @@
         <v>28</v>
       </c>
       <c r="G1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J1" t="s">
+        <v>104</v>
+      </c>
+      <c r="K1" t="s">
         <v>106</v>
-      </c>
-      <c r="H1" t="s">
-        <v>107</v>
-      </c>
-      <c r="I1" t="s">
-        <v>109</v>
-      </c>
-      <c r="J1" t="s">
-        <v>110</v>
-      </c>
-      <c r="K1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -2032,28 +2009,28 @@
         <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="H2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="I2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="J2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="K2">
         <v>8</v>
@@ -2064,31 +2041,31 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" t="s">
         <v>92</v>
       </c>
-      <c r="C3" t="s">
-        <v>98</v>
-      </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="J3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -2099,31 +2076,31 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" t="s">
         <v>93</v>
       </c>
-      <c r="C4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D4" t="s">
-        <v>99</v>
-      </c>
       <c r="E4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F4" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="J4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -2134,31 +2111,31 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" t="s">
         <v>94</v>
       </c>
-      <c r="C5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E5" t="s">
-        <v>100</v>
-      </c>
       <c r="F5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="J5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="K5">
         <v>2</v>
@@ -2169,31 +2146,31 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" t="s">
         <v>98</v>
       </c>
-      <c r="D6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F6" t="s">
-        <v>104</v>
-      </c>
       <c r="G6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="J6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="K6">
         <v>3</v>
@@ -2204,31 +2181,31 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F7" t="s">
         <v>99</v>
       </c>
-      <c r="E7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F7" t="s">
-        <v>105</v>
-      </c>
       <c r="G7" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H7" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I7" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="J7" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="K7">
         <v>20</v>
@@ -2239,44 +2216,35 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F8" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G8" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H8" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I8" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="J8" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K8">
         <v>100</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="29"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="30"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="30"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/features.xlsx
+++ b/features.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\uni\python\TBA_project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jakoberhard/Library/CloudStorage/GoogleDrive-jakanterh@gmail.com/My Drive/uni/python/TBA_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F57014-534C-42C9-A837-6BB0D22BF2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67B5BE3-3166-5E42-A5B2-2A783521C87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="10272" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="features" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="121">
   <si>
     <t>feature</t>
   </si>
@@ -371,6 +371,24 @@
   </si>
   <si>
     <t>above needed</t>
+  </si>
+  <si>
+    <t>actual delays</t>
+  </si>
+  <si>
+    <t>same day delay on station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stationen außerhalb deutschland </t>
+  </si>
+  <si>
+    <t>NA für bestimmte variablen (stops etc.)</t>
+  </si>
+  <si>
+    <t>modell fertigstellen</t>
+  </si>
+  <si>
+    <t>eventuell feature bauen</t>
   </si>
 </sst>
 </file>
@@ -712,7 +730,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -990,20 +1008,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:H47"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.83984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.41796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.83984375" customWidth="1"/>
-    <col min="4" max="4" width="22.5234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.26171875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="49.7890625" customWidth="1"/>
-    <col min="7" max="7" width="39.89453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="66.578125" customWidth="1"/>
+    <col min="1" max="1" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" customWidth="1"/>
+    <col min="4" max="4" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="49.83203125" customWidth="1"/>
+    <col min="7" max="7" width="39.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="157.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1029,7 +1047,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -1053,7 +1071,7 @@
       </c>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
@@ -1075,7 +1093,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>4</v>
       </c>
@@ -1095,7 +1113,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
@@ -1119,7 +1137,7 @@
       </c>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>37</v>
       </c>
@@ -1141,7 +1159,7 @@
       </c>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>49</v>
       </c>
@@ -1165,7 +1183,7 @@
       </c>
       <c r="H7" s="7"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
@@ -1189,7 +1207,7 @@
       </c>
       <c r="H8" s="7"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>36</v>
       </c>
@@ -1213,7 +1231,7 @@
       </c>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>8</v>
       </c>
@@ -1237,7 +1255,7 @@
       </c>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
@@ -1261,7 +1279,7 @@
       </c>
       <c r="H11" s="7"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>10</v>
       </c>
@@ -1285,7 +1303,7 @@
       </c>
       <c r="H12" s="7"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
@@ -1309,7 +1327,7 @@
       </c>
       <c r="H13" s="7"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
         <v>17</v>
       </c>
@@ -1333,7 +1351,7 @@
       </c>
       <c r="H14" s="7"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
         <v>18</v>
       </c>
@@ -1357,7 +1375,7 @@
       </c>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
         <v>19</v>
       </c>
@@ -1377,7 +1395,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>38</v>
       </c>
@@ -1397,7 +1415,7 @@
       <c r="G17" s="8"/>
       <c r="H17" s="9"/>
     </row>
-    <row r="18" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -1407,7 +1425,7 @@
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>82</v>
       </c>
@@ -1431,7 +1449,7 @@
       </c>
       <c r="H19" s="5"/>
     </row>
-    <row r="20" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>83</v>
       </c>
@@ -1455,7 +1473,7 @@
       </c>
       <c r="H20" s="9"/>
     </row>
-    <row r="21" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -1465,7 +1483,7 @@
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>28</v>
       </c>
@@ -1485,7 +1503,7 @@
       <c r="G22" s="4"/>
       <c r="H22" s="5"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="20" t="s">
         <v>110</v>
       </c>
@@ -1507,7 +1525,7 @@
       <c r="G23" s="2"/>
       <c r="H23" s="22"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>29</v>
       </c>
@@ -1533,7 +1551,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>30</v>
       </c>
@@ -1555,7 +1573,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>65</v>
       </c>
@@ -1579,7 +1597,7 @@
       </c>
       <c r="H26" s="7"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>64</v>
       </c>
@@ -1603,7 +1621,7 @@
       </c>
       <c r="H27" s="7"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>63</v>
       </c>
@@ -1627,7 +1645,7 @@
       </c>
       <c r="H28" s="7"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>57</v>
       </c>
@@ -1651,7 +1669,7 @@
       </c>
       <c r="H29" s="7"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>58</v>
       </c>
@@ -1675,7 +1693,7 @@
       </c>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>59</v>
       </c>
@@ -1699,7 +1717,7 @@
       </c>
       <c r="H31" s="7"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>60</v>
       </c>
@@ -1723,7 +1741,7 @@
       </c>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>61</v>
       </c>
@@ -1747,7 +1765,7 @@
       </c>
       <c r="H33" s="7"/>
     </row>
-    <row r="34" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>62</v>
       </c>
@@ -1771,7 +1789,7 @@
       </c>
       <c r="H34" s="9"/>
     </row>
-    <row r="35" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
@@ -1781,7 +1799,7 @@
       <c r="G35" s="27"/>
       <c r="H35" s="10"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>42</v>
       </c>
@@ -1805,7 +1823,7 @@
       </c>
       <c r="H36" s="5"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
         <v>48</v>
       </c>
@@ -1829,7 +1847,7 @@
       </c>
       <c r="H37" s="7"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
         <v>33</v>
       </c>
@@ -1853,7 +1871,7 @@
       </c>
       <c r="H38" s="7"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
         <v>35</v>
       </c>
@@ -1877,7 +1895,7 @@
       </c>
       <c r="H39" s="7"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
         <v>39</v>
       </c>
@@ -1901,7 +1919,7 @@
       </c>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
         <v>44</v>
       </c>
@@ -1925,7 +1943,7 @@
       </c>
       <c r="H41" s="7"/>
     </row>
-    <row r="42" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>45</v>
       </c>
@@ -1948,6 +1966,30 @@
         <v>114</v>
       </c>
       <c r="H42" s="9"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>120</v>
+      </c>
+      <c r="B44" t="s">
+        <v>115</v>
+      </c>
+      <c r="C44" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>117</v>
+      </c>
+      <c r="B45" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>119</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1957,16 +1999,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E59CFC8-413C-463C-B177-BDA848B5E119}">
   <dimension ref="A1:K8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.62890625" customWidth="1"/>
-    <col min="5" max="6" width="13.734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.9453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.1015625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7890625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" customWidth="1"/>
+    <col min="5" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2001,7 +2043,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2036,7 +2078,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2071,7 +2113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2106,7 +2148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2141,7 +2183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
@@ -2176,7 +2218,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
@@ -2211,7 +2253,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>

--- a/features.xlsx
+++ b/features.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jakoberhard/Library/CloudStorage/GoogleDrive-jakanterh@gmail.com/My Drive/uni/python/TBA_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67B5BE3-3166-5E42-A5B2-2A783521C87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29E5851-0560-E84E-9C3A-10DD19C89B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="116">
   <si>
     <t>feature</t>
   </si>
@@ -181,15 +181,6 @@
     <t>station_related_history</t>
   </si>
   <si>
-    <t>group by station and give delay (mean)</t>
-  </si>
-  <si>
-    <t>group by station and give delay (sd)</t>
-  </si>
-  <si>
-    <t>group by station and give q90 quantile of delay</t>
-  </si>
-  <si>
     <t>see above only for specific day</t>
   </si>
   <si>
@@ -199,33 +190,6 @@
     <t>start / stopover / destination</t>
   </si>
   <si>
-    <t>hist_delay_avg_station * day</t>
-  </si>
-  <si>
-    <t>hist_delay_sd_station * day</t>
-  </si>
-  <si>
-    <t>hist_delay_q9_station * day</t>
-  </si>
-  <si>
-    <t>hist_delay_avg_station * hour</t>
-  </si>
-  <si>
-    <t>hist_delay_sd_station * hour</t>
-  </si>
-  <si>
-    <t>hist_delay_q9_station * hour</t>
-  </si>
-  <si>
-    <t>hist_delay_q9_station</t>
-  </si>
-  <si>
-    <t>hist_delay_sd_station</t>
-  </si>
-  <si>
-    <t>hist_delay_avg_station</t>
-  </si>
-  <si>
     <t>availability historical data</t>
   </si>
   <si>
@@ -235,9 +199,6 @@
     <t>not needed</t>
   </si>
   <si>
-    <t>? (@eddi)</t>
-  </si>
-  <si>
     <t>variable not needed</t>
   </si>
   <si>
@@ -389,6 +350,30 @@
   </si>
   <si>
     <t>eventuell feature bauen</t>
+  </si>
+  <si>
+    <t>hour</t>
+  </si>
+  <si>
+    <t>indicating time of the day</t>
+  </si>
+  <si>
+    <t>hist_delay_station_avg/sd/q90/count</t>
+  </si>
+  <si>
+    <t>hist_delay_station_day_avg/sd/q90/count</t>
+  </si>
+  <si>
+    <t>hist_delay_station_hour_avg/sd/q90/count</t>
+  </si>
+  <si>
+    <t>group by station and give delay (mean/sd/q90/count)</t>
+  </si>
+  <si>
+    <t>count is added as indicator data quality</t>
+  </si>
+  <si>
+    <t>canceled</t>
   </si>
 </sst>
 </file>
@@ -699,7 +684,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -728,6 +713,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1008,10 +994,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.6640625" customWidth="1"/>
     <col min="4" max="4" width="22.5" bestFit="1" customWidth="1"/>
@@ -1032,19 +1018,19 @@
         <v>1</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -1057,17 +1043,17 @@
       <c r="C2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>69</v>
+      <c r="D2" s="15" t="s">
+        <v>55</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H2" s="5"/>
     </row>
@@ -1082,15 +1068,15 @@
         <v>20</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="7" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -1104,10 +1090,10 @@
         <v>20</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -1123,17 +1109,17 @@
       <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="15" t="s">
         <v>22</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="H5" s="7"/>
     </row>
@@ -1148,68 +1134,64 @@
         <v>20</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="D7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
       <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="15" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>13</v>
@@ -1217,95 +1199,95 @@
       <c r="C9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="15" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="15" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="15" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="15" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>15</v>
@@ -1313,47 +1295,47 @@
       <c r="C13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="15" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="15" t="s">
         <v>22</v>
       </c>
       <c r="E14" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
@@ -1361,269 +1343,267 @@
       <c r="C15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="15" t="s">
         <v>22</v>
       </c>
       <c r="E15" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
+      <c r="D16" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B18" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C18" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B19" s="4" t="s">
+      <c r="D18" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="9"/>
+    </row>
+    <row r="19" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" s="4" t="s">
+      <c r="C20" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="B20" s="8" t="s">
+      <c r="D20" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="8" t="s">
+      <c r="C21" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+      <c r="D21" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H21" s="9"/>
+    </row>
+    <row r="22" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B23" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C23" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="5"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="D23" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="22"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>108</v>
-      </c>
+      <c r="D24" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="22"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="17" t="s">
-        <v>86</v>
+      <c r="D25" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
+        <v>60</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="H25" s="7" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D26" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H26" s="7"/>
+        <v>21</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="7" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D27" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H27" s="7"/>
+        <v>21</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="7" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>12</v>
@@ -1631,23 +1611,25 @@
       <c r="C28" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="23" t="s">
+      <c r="D28" s="15" t="s">
         <v>22</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H28" s="7"/>
+        <v>72</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>12</v>
@@ -1655,177 +1637,177 @@
       <c r="C29" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="23" t="s">
+      <c r="D29" s="15" t="s">
         <v>22</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="H29" s="7"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" s="1" t="s">
+    <row r="30" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H30" s="7"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H31" s="7"/>
+      <c r="D30" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H30" s="9"/>
+    </row>
+    <row r="31" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="10"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H32" s="7"/>
+      <c r="A32" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H32" s="5"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>68</v>
+        <v>32</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>22</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>85</v>
+        <v>34</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="H33" s="7"/>
     </row>
-    <row r="34" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H34" s="7"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B34" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D34" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="10"/>
+      <c r="H35" s="7"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="4" t="s">
+      <c r="A36" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D36" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="E36" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="H36" s="5"/>
+      <c r="D36" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H36" s="7"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>12</v>
@@ -1833,162 +1815,66 @@
       <c r="C37" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="23" t="s">
+      <c r="D37" s="15" t="s">
         <v>22</v>
       </c>
       <c r="E37" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>113</v>
+        <v>43</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="H37" s="7"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38" s="1" t="s">
+    <row r="38" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E38" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H38" s="7"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H39" s="7"/>
+      <c r="D38" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="H38" s="9"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D40" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E40" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H40" s="7"/>
+      <c r="A40" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" t="s">
+        <v>102</v>
+      </c>
+      <c r="C40" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D41" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E41" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H41" s="7"/>
-    </row>
-    <row r="42" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D42" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="E42" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>120</v>
-      </c>
-      <c r="B44" t="s">
-        <v>115</v>
-      </c>
-      <c r="C44" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>117</v>
-      </c>
-      <c r="B45" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>119</v>
+      <c r="A41" t="s">
+        <v>104</v>
+      </c>
+      <c r="B41" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2028,19 +1914,19 @@
         <v>28</v>
       </c>
       <c r="G1" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="H1" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="I1" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="J1" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="K1" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -2048,31 +1934,31 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="H2" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="I2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="J2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="K2">
         <v>8</v>
@@ -2083,31 +1969,31 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="F3" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G3" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="H3" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="I3" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="J3" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -2118,31 +2004,31 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="F4" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="G4" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="H4" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="I4" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="J4" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -2153,31 +2039,31 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="F5" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G5" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="H5" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="I5" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="J5" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="K5">
         <v>2</v>
@@ -2188,31 +2074,31 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="F6" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="G6" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="I6" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="J6" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="K6">
         <v>3</v>
@@ -2223,31 +2109,31 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="F7" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="G7" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="I7" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="J7" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="K7">
         <v>20</v>
@@ -2258,31 +2144,31 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="F8" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="H8" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="I8" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="J8" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="K8">
         <v>100</v>

--- a/features.xlsx
+++ b/features.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jakoberhard/Library/CloudStorage/GoogleDrive-jakanterh@gmail.com/My Drive/uni/python/TBA_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29E5851-0560-E84E-9C3A-10DD19C89B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33761C64-A4DC-E84C-B233-6FCA27BB99F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="107">
   <si>
     <t>feature</t>
   </si>
@@ -148,12 +148,6 @@
     <t>time_till_dest_planned</t>
   </si>
   <si>
-    <t>arrival_current_station - depature_first_station</t>
-  </si>
-  <si>
-    <t>arrival_last_station - depature_current_station</t>
-  </si>
-  <si>
     <t>station_role</t>
   </si>
   <si>
@@ -232,18 +226,6 @@
     <t>availability api data</t>
   </si>
   <si>
-    <t>route_related_history</t>
-  </si>
-  <si>
-    <t>hist_delay_avg_route</t>
-  </si>
-  <si>
-    <t>hist_delay_sd_route</t>
-  </si>
-  <si>
-    <t>group all connections that have common start station and current station (trains coming from X, how much delay do they have at Y?)</t>
-  </si>
-  <si>
     <t>from historical data (saved from training)</t>
   </si>
   <si>
@@ -289,21 +271,12 @@
     <t>Halt 5</t>
   </si>
   <si>
-    <t>arrival_planned</t>
-  </si>
-  <si>
     <t>arrival_real</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t>depature_planned</t>
-  </si>
-  <si>
-    <t>depature_real</t>
-  </si>
-  <si>
     <t>ZEIT</t>
   </si>
   <si>
@@ -319,9 +292,6 @@
     <t>we can leave the weather for every station out, this would reduce complexity because we then only have 2 weather api calls for every train ride</t>
   </si>
   <si>
-    <t>time_current_planned</t>
-  </si>
-  <si>
     <t>planned_depature</t>
   </si>
   <si>
@@ -334,24 +304,6 @@
     <t>above needed</t>
   </si>
   <si>
-    <t>actual delays</t>
-  </si>
-  <si>
-    <t>same day delay on station</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stationen außerhalb deutschland </t>
-  </si>
-  <si>
-    <t>NA für bestimmte variablen (stops etc.)</t>
-  </si>
-  <si>
-    <t>modell fertigstellen</t>
-  </si>
-  <si>
-    <t>eventuell feature bauen</t>
-  </si>
-  <si>
     <t>hour</t>
   </si>
   <si>
@@ -374,6 +326,27 @@
   </si>
   <si>
     <t>canceled</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>time_current_arrival_planned</t>
+  </si>
+  <si>
+    <t>time_current_departure_planned</t>
+  </si>
+  <si>
+    <t>time_current__departure_real</t>
+  </si>
+  <si>
+    <t>time_current_departure_real</t>
+  </si>
+  <si>
+    <t>arrival_current_station - departure_first_station</t>
+  </si>
+  <si>
+    <t>arrival_last_station - departure_current_station</t>
   </si>
 </sst>
 </file>
@@ -684,7 +657,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -714,6 +687,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -994,7 +968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.6640625" bestFit="1" customWidth="1"/>
@@ -1018,19 +992,19 @@
         <v>1</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -1044,16 +1018,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="H2" s="5"/>
     </row>
@@ -1068,15 +1042,15 @@
         <v>20</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -1090,10 +1064,10 @@
         <v>20</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -1113,13 +1087,13 @@
         <v>22</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H5" s="7"/>
     </row>
@@ -1134,20 +1108,20 @@
         <v>20</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>15</v>
@@ -1156,10 +1130,10 @@
         <v>20</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -1167,7 +1141,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>12</v>
@@ -1185,7 +1159,7 @@
         <v>26</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H8" s="7"/>
     </row>
@@ -1209,7 +1183,7 @@
         <v>23</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H9" s="7"/>
     </row>
@@ -1233,7 +1207,7 @@
         <v>24</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H10" s="7"/>
     </row>
@@ -1257,7 +1231,7 @@
         <v>25</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H11" s="7"/>
     </row>
@@ -1278,10 +1252,10 @@
         <v>22</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H12" s="7"/>
     </row>
@@ -1302,10 +1276,10 @@
         <v>22</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H13" s="7"/>
     </row>
@@ -1326,10 +1300,10 @@
         <v>22</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H14" s="7"/>
     </row>
@@ -1350,10 +1324,10 @@
         <v>22</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H15" s="7"/>
     </row>
@@ -1374,10 +1348,10 @@
         <v>22</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H16" s="7"/>
     </row>
@@ -1392,10 +1366,10 @@
         <v>20</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -1412,10 +1386,10 @@
         <v>20</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
@@ -1433,110 +1407,118 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>72</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
       <c r="H20" s="5"/>
     </row>
-    <row r="21" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="22"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="22"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="4" t="s">
+      <c r="A23" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="5"/>
+      <c r="D23" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="22"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="A24" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="22"/>
+      <c r="D24" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>21</v>
@@ -1544,174 +1526,172 @@
       <c r="D25" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>94</v>
-      </c>
+      <c r="E25" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
       <c r="H25" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>22</v>
+      <c r="D26" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>67</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="7" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="H27" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H28" s="7"/>
+    </row>
+    <row r="29" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B29" s="1" t="s">
+      <c r="G29" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H29" s="9"/>
+    </row>
+    <row r="30" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="10"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H31" s="5"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H29" s="7"/>
-    </row>
-    <row r="30" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D30" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="10"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E32" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="H32" s="5"/>
+      <c r="D32" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H32" s="7"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>12</v>
@@ -1726,19 +1706,19 @@
         <v>22</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>100</v>
+        <v>45</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H33" s="7"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>32</v>
@@ -1750,16 +1730,16 @@
         <v>22</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H34" s="7"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>14</v>
@@ -1774,19 +1754,19 @@
         <v>22</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H35" s="7"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>32</v>
@@ -1801,81 +1781,33 @@
         <v>41</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="H36" s="7"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
+    <row r="37" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E37" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H37" s="7"/>
-    </row>
-    <row r="38" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E38" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>107</v>
-      </c>
-      <c r="B40" t="s">
-        <v>102</v>
-      </c>
-      <c r="C40" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>104</v>
-      </c>
-      <c r="B41" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>106</v>
-      </c>
+      <c r="G37" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H37" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1884,28 +1816,29 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E59CFC8-413C-463C-B177-BDA848B5E119}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
     <col min="5" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
       </c>
       <c r="E1" t="s">
         <v>37</v>
@@ -1914,263 +1847,287 @@
         <v>28</v>
       </c>
       <c r="G1" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="H1" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="I1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J1" t="s">
-        <v>91</v>
+        <v>81</v>
+      </c>
+      <c r="J1" s="29" t="s">
+        <v>102</v>
       </c>
       <c r="K1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+      <c r="L1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" t="s">
+        <v>83</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I4" t="s">
+        <v>83</v>
+      </c>
+      <c r="J4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" t="s">
         <v>78</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" t="s">
+        <v>83</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" t="s">
         <v>79</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>83</v>
+      </c>
+      <c r="I6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" t="s">
         <v>80</v>
       </c>
-      <c r="E2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I2" t="s">
-        <v>92</v>
-      </c>
-      <c r="J2" t="s">
-        <v>92</v>
-      </c>
-      <c r="K2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I7" t="s">
+        <v>83</v>
+      </c>
+      <c r="J7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" t="s">
+        <v>83</v>
+      </c>
+      <c r="L7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J8" t="s">
         <v>82</v>
       </c>
-      <c r="G3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I3" t="s">
-        <v>92</v>
-      </c>
-      <c r="J3" t="s">
-        <v>92</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H4" t="s">
-        <v>92</v>
-      </c>
-      <c r="I4" t="s">
-        <v>92</v>
-      </c>
-      <c r="J4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G5" t="s">
-        <v>92</v>
-      </c>
-      <c r="H5" t="s">
-        <v>92</v>
-      </c>
-      <c r="I5" t="s">
-        <v>92</v>
-      </c>
-      <c r="J5" t="s">
-        <v>92</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F6" t="s">
-        <v>85</v>
-      </c>
-      <c r="G6" t="s">
-        <v>92</v>
-      </c>
-      <c r="H6" t="s">
-        <v>92</v>
-      </c>
-      <c r="I6" t="s">
-        <v>92</v>
-      </c>
-      <c r="J6" t="s">
-        <v>92</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F7" t="s">
-        <v>86</v>
-      </c>
-      <c r="G7" t="s">
-        <v>92</v>
-      </c>
-      <c r="H7" t="s">
-        <v>92</v>
-      </c>
-      <c r="I7" t="s">
-        <v>92</v>
-      </c>
-      <c r="J7" t="s">
-        <v>92</v>
-      </c>
-      <c r="K7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" t="s">
-        <v>81</v>
-      </c>
-      <c r="F8" t="s">
-        <v>81</v>
-      </c>
-      <c r="G8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H8" t="s">
-        <v>92</v>
-      </c>
-      <c r="I8" t="s">
-        <v>89</v>
-      </c>
-      <c r="J8" t="s">
-        <v>89</v>
-      </c>
-      <c r="K8">
+      <c r="K8" t="s">
+        <v>82</v>
+      </c>
+      <c r="L8">
         <v>100</v>
       </c>
     </row>

--- a/features.xlsx
+++ b/features.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jakoberhard/Library/CloudStorage/GoogleDrive-jakanterh@gmail.com/My Drive/uni/python/TBA_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33761C64-A4DC-E84C-B233-6FCA27BB99F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866C2C2E-F4D3-754A-B578-497F3D14ABCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="features" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="98">
   <si>
     <t>feature</t>
   </si>
@@ -46,9 +46,6 @@
     <t>station_start</t>
   </si>
   <si>
-    <t>time_start_planned</t>
-  </si>
-  <si>
     <t>category</t>
   </si>
   <si>
@@ -58,9 +55,6 @@
     <t>weekday</t>
   </si>
   <si>
-    <t>weekend</t>
-  </si>
-  <si>
     <t>pandas data_type</t>
   </si>
   <si>
@@ -82,12 +76,6 @@
     <t>month</t>
   </si>
   <si>
-    <t>season</t>
-  </si>
-  <si>
-    <t>weather_start</t>
-  </si>
-  <si>
     <t>ride_related</t>
   </si>
   <si>
@@ -118,36 +106,21 @@
     <t>dwell_time_planned</t>
   </si>
   <si>
-    <t>weather_current</t>
-  </si>
-  <si>
     <t xml:space="preserve">planned_depature - planned_arrival </t>
   </si>
   <si>
     <t>sequence_related</t>
   </si>
   <si>
-    <t>stops_remaining</t>
-  </si>
-  <si>
     <t>row number grouped by unique ride</t>
   </si>
   <si>
     <t>time_since_start_planned</t>
   </si>
   <si>
-    <t>time_dest_planned</t>
-  </si>
-  <si>
     <t>station_dest</t>
   </si>
   <si>
-    <t>weather_dest</t>
-  </si>
-  <si>
-    <t>time_till_dest_planned</t>
-  </si>
-  <si>
     <t>station_role</t>
   </si>
   <si>
@@ -157,15 +130,6 @@
     <t>share_ride_time</t>
   </si>
   <si>
-    <t>share_ride_stations</t>
-  </si>
-  <si>
-    <t>stops_index / stops_total</t>
-  </si>
-  <si>
-    <t>stops_total - stops_index - 1</t>
-  </si>
-  <si>
     <t>stops_index</t>
   </si>
   <si>
@@ -178,9 +142,6 @@
     <t>see above only for specific day</t>
   </si>
   <si>
-    <t>see above only for specific hour</t>
-  </si>
-  <si>
     <t>start / stopover / destination</t>
   </si>
   <si>
@@ -340,13 +301,25 @@
     <t>time_current__departure_real</t>
   </si>
   <si>
-    <t>time_current_departure_real</t>
-  </si>
-  <si>
     <t>arrival_current_station - departure_first_station</t>
   </si>
   <si>
-    <t>arrival_last_station - departure_current_station</t>
+    <t>departure_planned</t>
+  </si>
+  <si>
+    <t>arrival_planned</t>
+  </si>
+  <si>
+    <t>departure_planned_start</t>
+  </si>
+  <si>
+    <t>arrival_planned_dest</t>
+  </si>
+  <si>
+    <t>weather</t>
+  </si>
+  <si>
+    <t>group by station/hour and give delay (mean/sd/q90/count)</t>
   </si>
 </sst>
 </file>
@@ -657,7 +630,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -687,7 +660,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -968,7 +940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.6640625" bestFit="1" customWidth="1"/>
@@ -986,25 +958,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="13" t="s">
-        <v>65</v>
-      </c>
       <c r="F1" s="13" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -1012,22 +984,22 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H2" s="5"/>
     </row>
@@ -1036,21 +1008,21 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="7" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -1058,16 +1030,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -1078,136 +1050,140 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H5" s="7"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="H10" s="7"/>
     </row>
@@ -1216,598 +1192,414 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
+      <c r="C14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="D14" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="9"/>
+    </row>
+    <row r="15" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H16" s="7"/>
+      <c r="D16" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="1" t="s">
+      <c r="A17" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="22"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="22"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="C19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H23" s="7"/>
+    </row>
+    <row r="24" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H24" s="9"/>
+    </row>
+    <row r="25" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="10"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="22"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="22"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="22"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="7" t="s">
-        <v>87</v>
-      </c>
+      <c r="G26" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>54</v>
+        <v>18</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>18</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>98</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H27" s="7"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>54</v>
+        <v>18</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>18</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="H28" s="7"/>
     </row>
     <row r="29" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>54</v>
+        <v>18</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>18</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="10"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H31" s="5"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H32" s="7"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H33" s="7"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E34" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H34" s="7"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E35" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H35" s="7"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H36" s="7"/>
-    </row>
-    <row r="37" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D37" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E37" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="H37" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1829,7 +1621,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
@@ -1841,28 +1633,28 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G1" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="H1" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="I1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J1" s="29" t="s">
-        <v>102</v>
+        <v>68</v>
+      </c>
+      <c r="J1" t="s">
+        <v>89</v>
       </c>
       <c r="K1" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="L1" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -1873,31 +1665,31 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F2" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="I2" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="J2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="K2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="L2">
         <v>8</v>
@@ -1911,31 +1703,31 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="I3" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="J3" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="K3" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -1949,31 +1741,31 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="I4" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="J4" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="K4" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -1987,31 +1779,31 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="I5" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="J5" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="K5" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -2025,31 +1817,31 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="I6" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="J6" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="K6" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -2063,31 +1855,31 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="I7" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="J7" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="K7" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="L7">
         <v>20</v>
@@ -2101,31 +1893,31 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="I8" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="J8" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="K8" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="L8">
         <v>100</v>

--- a/features.xlsx
+++ b/features.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jakoberhard/Library/CloudStorage/GoogleDrive-jakanterh@gmail.com/My Drive/uni/python/TBA_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866C2C2E-F4D3-754A-B578-497F3D14ABCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366098B6-38E1-6344-8957-938B48DDD896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/features.xlsx
+++ b/features.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jakoberhard/Library/CloudStorage/GoogleDrive-jakanterh@gmail.com/My Drive/uni/python/TBA_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366098B6-38E1-6344-8957-938B48DDD896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6464CF0D-601B-344C-8546-903A961C1A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1120,7 +1120,7 @@
         <v>94</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>16</v>
@@ -1144,7 +1144,7 @@
         <v>95</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>16</v>
